--- a/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé est au parc avec papa. Elle sculpte un château dans le bac à sable. Un ballon roule tout près. Le château s'affaisse d'un coup. Zoé sent son visage brûler. Ses mains deviennent chaudes et dures. Zoé dit : je suis en colère. Elle ouvre les doigts. Elle garde les mains loin de l'autre enfant. Zoé peut s'éloigner. Elle s'éloigne du bac à sable. Elle va sous le tilleul. Elle souffle quatre fois, lentement. Puis elle marche vers papa. Papa est l'adulte assis au banc. Zoé dit : papa, je suis en colère. Le château est tombé. Papa écoute. Zoé reste près de lui. Plus tard, elles refont un petit tas. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Zoé est au parc avec papa. Elle sculpte un château dans le bac à sable. Un ballon roule tout près. Le château s'affaisse d'un coup. Zoé sent son visage brûler. Ses mains deviennent chaudes et dures. Je suis en colère. Elle ouvre les doigts. Elle garde les mains loin de l'autre enfant. Zoé peut s'éloigner. Elle s'éloigne du bac à sable. Elle va sous le tilleul. Elle souffle quatre fois, lentement. Puis elle marche vers papa. Papa est l'adulte assis au banc. Papa, je suis en colère. Le château est tombé. Papa écoute. Zoé reste près de lui. Plus tard, elles refont un petit tas. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé est au parc avec papa. Elle sculpte un château dans le bac à sable. Un ballon roule tout près. Le château s'affaisse d'un coup. Zoé sent son visage brûler. Ses mains deviennent chaudes et dures.
+enfant-f|Je suis en colère. Elle ouvre les doigts. Elle garde les mains loin de l'autre enfant.
+narrateur|Zoé peut s'éloigner. Elle s'éloigne du bac à sable. Elle va sous le tilleul. Elle souffle quatre fois, lentement. Puis elle marche vers papa. Papa est l'adulte assis au banc.
+enfant-f|Papa, je suis en colère.
+narrateur|Le château est tombé. Papa écoute. Zoé reste près de lui. Plus tard, elles refont un petit tas. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le château de Zoé s'affaisse. Que fait-elle de sa colère ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a nommé sa colère au parc. Mains loin. Elle peut s'éloigner. Elle rejoint papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé pose une coquille sur le petit tas. Papa reste au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Le château est tombé. Papa écoute. Zoé reste près de lui. Plus tard, elles refont un petit tas. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Le château de Zoé s'affaisse. Que fait-elle de sa colère ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,11 @@
           <t>narrateur|Zoé a nommé sa colère au parc. Mains loin. Elle peut s'éloigner. Elle rejoint papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1851,7 @@
           <t>narrateur|Zoé pose une coquille sur le petit tas. Papa reste au banc.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Être en colère</t>
+          <t>Chouchou et le château de sable</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le château de Chouchou s'affaisse. Il nomme sa colère. Mains loin. Il s'éloigne. Il rejoint papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé est au parc avec papa. Elle sculpte un château dans le bac à sable. Un ballon roule tout près. Le château s'affaisse d'un coup. Zoé sent son visage brûler. Ses mains deviennent chaudes et dures. Je suis en colère. Elle ouvre les doigts. Elle garde les mains loin de l'autre enfant. Zoé peut s'éloigner. Elle s'éloigne du bac à sable. Elle va sous le tilleul. Elle souffle quatre fois, lentement. Puis elle marche vers papa. Papa est l'adulte assis au banc. Papa, je suis en colère. Le château est tombé. Papa écoute. Zoé reste près de lui. Plus tard, elles refont un petit tas. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Le tilleul fait une ombre ronde. Le sable est tiède. Une balançoire grince au loin. Un seau rouge attend dans le bac. Une fourmi croise le sable. Le vent bouge les feuilles. Papa s'assoit au banc. Le sable sent le soleil. Chouchou, tu prends le seau ? Oui. Je fais un château. Tout doux, avec les mains. En ce moment, Chouchou sculpte un château. Le château a une petite tour. Un ballon roule tout près. Le château s'affaisse d'un coup. Chouchou sent son visage brûler. Ses mains deviennent chaudes. Je suis en colère. Il ouvre les doigts. Il garde les mains loin. Les mains restent loin. Chouchou peut s'éloigner. Il s'éloigne du bac à sable. Il va sous le tilleul. Il souffle quatre fois, lentement. Tu as soufflé. Bravo. Tu peux venir vers moi. Chouchou marche vers papa. Papa est l'adulte assis au banc. Papa, je suis en colère. Je t'écoute. Le château est tombé. Tu as nommé. Tu t'es éloigné. Plus tard, on refait un petit tas. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte. Tu as soufflé sous le tilleul. Quatre fois. Lentement. Bravo, Chouchou. Le tilleul bouge un peu. Le seau rouge attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Zoé est au parc avec papa. Elle sculpte un château dans le bac à sable. Un ballon roule tout près. Le château s'affaisse d'un coup. Zoé sent son visage brûler. Ses mains deviennent chaudes et dures.
-enfant-f|Je suis en colère. Elle ouvre les doigts. Elle garde les mains loin de l'autre enfant.
-narrateur|Zoé peut s'éloigner. Elle s'éloigne du bac à sable. Elle va sous le tilleul. Elle souffle quatre fois, lentement. Puis elle marche vers papa. Papa est l'adulte assis au banc.
-enfant-f|Papa, je suis en colère.
-narrateur|Le château est tombé. Papa écoute. Zoé reste près de lui. Plus tard, elles refont un petit tas. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>narrateur|Le tilleul fait une ombre ronde.
+narrateur|Le sable est tiède.
+narrateur|Une balançoire grince au loin.
+narrateur|Un seau rouge attend dans le bac.
+narrateur|Une fourmi croise le sable.
+narrateur|Le vent bouge les feuilles.
+narrateur|Papa s'assoit au banc.
+maman|Le sable sent le soleil.
+papa|Chouchou, tu prends le seau ?
+enfant-m|Oui. Je fais un château.
+maman|Tout doux, avec les mains.
+narrateur|En ce moment, Chouchou sculpte un château.
+narrateur|Le château a une petite tour.
+narrateur|Un ballon roule tout près.
+narrateur|Le château s'affaisse d'un coup.
+narrateur|Chouchou sent son visage brûler.
+narrateur|Ses mains deviennent chaudes.
+enfant-m|Je suis en colère.
+narrateur|Il ouvre les doigts.
+narrateur|Il garde les mains loin.
+papa|Les mains restent loin.
+narrateur|Chouchou peut s'éloigner.
+narrateur|Il s'éloigne du bac à sable.
+narrateur|Il va sous le tilleul.
+narrateur|Il souffle quatre fois, lentement.
+maman|Tu as soufflé. Bravo.
+papa|Tu peux venir vers moi.
+narrateur|Chouchou marche vers papa.
+narrateur|Papa est l'adulte assis au banc.
+enfant-m|Papa, je suis en colère.
+papa|Je t'écoute.
+enfant-m|Le château est tombé.
+maman|Tu as nommé. Tu t'es éloigné.
+papa|Plus tard, on refait un petit tas.
+narrateur|La colère a un nom.
+narrateur|Les mains restent loin.
+narrateur|On s'éloigne.
+narrateur|On va vers un adulte.
+maman|Tu as soufflé sous le tilleul.
+enfant-m|Quatre fois. Lentement.
+papa|Bravo, Chouchou.
+narrateur|Le tilleul bouge un peu.
+narrateur|Le seau rouge attend encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le château de Zoé s'affaisse. Que fait-elle de sa colère ?</t>
+          <t>Le château de Chouchou s'affaisse. Que fait-il de sa colère ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le château de Zoé s'affaisse. Que fait-elle de sa colère ?</t>
+          <t>narrateur|Le château de Chouchou s'affaisse.
+narrateur|Que fait-il de sa colère ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zoé a nommé sa colère au parc. Mains loin. Elle peut s'éloigner. Elle rejoint papa, l'adulte.</t>
+          <t>Chouchou a nommé sa colère au parc. Mains loin. Il peut s'éloigner. Il rejoint papa, l'adulte. Tu as soufflé. Bravo. Tu es venu vers le banc. Je suis en colère. C'est dit. Les mains restent loin. C'est bien. Tu es allé sous le tilleul. Puis vers papa, l'adulte. Le seau rouge attend encore. Le sable est toujours tiède. Plus tard, un petit tas. La fourmi croise encore le sable.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1731,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a nommé sa colère au parc. Mains loin. Elle peut s'éloigner. Elle rejoint papa, l'adulte.</t>
+          <t>narrateur|Chouchou a nommé sa colère au parc.
+narrateur|Mains loin.
+narrateur|Il peut s'éloigner.
+narrateur|Il rejoint papa, l'adulte.
+papa|Tu as soufflé. Bravo.
+maman|Tu es venu vers le banc.
+enfant-m|Je suis en colère. C'est dit.
+papa|Les mains restent loin. C'est bien.
+maman|Tu es allé sous le tilleul.
+enfant-m|Puis vers papa, l'adulte.
+narrateur|Le seau rouge attend encore.
+narrateur|Le sable est toujours tiède.
+papa|Plus tard, un petit tas.
+narrateur|La fourmi croise encore le sable.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1712,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Zoé pose une coquille sur le petit tas. Papa reste au banc.</t>
+          <t>Chouchou pose une coquille sur le petit tas. Papa reste au banc. La coquille est lisse. Oui. Elle est blanche. Tu as nommé. Tu t'es éloigné. Je suis plus calme. On va vers un adulte. C'est bien. On laisse le seau dans le bac ? Oui. Près du petit tas. La balançoire grince encore. L'ombre du tilleul est ronde. Le vent bouge encore les feuilles.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1848,10 +1912,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Zoé pose une coquille sur le petit tas. Papa reste au banc.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Chouchou pose une coquille sur le petit tas.
+narrateur|Papa reste au banc.
+maman|La coquille est lisse.
+enfant-m|Oui. Elle est blanche.
+papa|Tu as nommé. Tu t'es éloigné.
+enfant-m|Je suis plus calme.
+maman|On va vers un adulte. C'est bien.
+papa|On laisse le seau dans le bac ?
+enfant-m|Oui. Près du petit tas.
+narrateur|La balançoire grince encore.
+narrateur|L'ombre du tilleul est ronde.
+narrateur|Le vent bouge encore les feuilles.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais en colère. Je suis allé vers papa. Tes mains étaient loin. Bravo. Le tilleul faisait de l'ombre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2016,7 +2095,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais en colère. Je suis allé vers papa.
+papa|Tes mains étaient loin. Bravo.
+maman|Le tilleul faisait de l'ombre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2038,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé est au parc avec papa. Elle sculpte un château dans le bac à sable. Un ballon roule tout près. Le château s'affaisse d'un coup. Zoé sent son visage brûler. Ses mains deviennent chaudes et dures. Zoé dit : je suis en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Elle ouvre les doigts. Elle garde les mains loin de l'autre enfant. Zoé peut s'éloigner. Elle s'éloigne du bac à sable. Elle va sous le tilleul. Elle souffle quatre fois, lentement. Puis elle marche vers papa. Papa est l'adulte assis au banc. Zoé dit : papa, je suis en colère. Le château est tombé. Papa écoute. Zoé reste près de lui. Plus tard, elles refont un petit tas. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le tilleul fait une ombre ronde. Le sable est tiède. Une balançoire grince au loin. Un seau rouge attend dans le bac. Une fourmi croise le sable. Le vent bouge les feuilles. Papa s'assoit au banc. Le sable sent le soleil. Chouchou, tu prends le seau ? Oui. Je fais un château. Tout doux, avec les mains. En ce moment, Chouchou sculpte un château. Le château a une petite tour. Un ballon roule tout près. Le château s'affaisse d'un coup. Chouchou sent son visage brûler. Ses mains deviennent chaudes. Je suis en colère. Il ouvre les doigts. Il garde les mains loin. Les mains restent loin. Chouchou peut s'éloigner. Il s'éloigne du bac à sable. Il va sous le tilleul. Il souffle quatre fois, lentement. Tu as soufflé. Bravo. Tu peux venir vers moi. Chouchou marche vers papa. Papa est l'adulte assis au banc. Papa, je suis en colère. Je t'écoute. Le château est tombé. Tu as nommé. Tu t'es éloigné. Plus tard, on refait un petit tas. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte. Tu as soufflé sous le tilleul. Quatre fois. Lentement. Bravo, Chouchou. Le tilleul bouge un peu. Le seau rouge attend encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le château de Zoé s'affaisse. Que fait-elle de sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le château de Chouchou s'affaisse. Que fait-il de sa colère ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1562,6 @@
 narrateur|Que fait-il de sa colère ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,7 +1591,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé a nommé sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt; au parc. Mains loin. Elle peut s'éloigner. Elle rejoint papa, l'adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a nommé sa colère au parc. Mains loin. Il peut s'éloigner. Il rejoint papa, l'adulte. Tu as soufflé. Bravo. Tu es venu vers le banc. Je suis en colère. C'est dit. Les mains restent loin. C'est bien. Tu es allé sous le tilleul. Puis vers papa, l'adulte. Le seau rouge attend encore. Le sable est toujours tiède. Plus tard, un petit tas. La fourmi croise encore le sable.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1781,7 +1780,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé pose une coquille sur le petit tas. Papa reste au banc.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou pose une coquille sur le petit tas. Papa reste au banc. La coquille est lisse. Oui. Elle est blanche. Tu as nommé. Tu t'es éloigné. Je suis plus calme. On va vers un adulte. C'est bien. On laisse le seau dans le bac ? Oui. Près du petit tas. La balançoire grince encore. L'ombre du tilleul est ronde. Le vent bouge encore les feuilles.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1955,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais en colère. Je suis allé vers papa. Tes mains étaient loin. Bravo. Le tilleul faisait de l'ombre. L'histoire est finie.</t>
+          <t>J'étais en colère. Je suis allé vers papa. Tes mains étaient loin. Bravo. Le tilleul faisait de l'ombre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais en colère. Je suis allé vers papa. Tes mains étaient loin. Bravo. Le tilleul faisait de l'ombre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,11 +2096,9 @@
         <is>
           <t>enfant-m|J'étais en colère. Je suis allé vers papa.
 papa|Tes mains étaient loin. Bravo.
-maman|Le tilleul faisait de l'ombre.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Le tilleul faisait de l'ombre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2120,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zoé, papa</t>
+          <t>Chouchou, papa, maman</t>
         </is>
       </c>
     </row>
